--- a/timetable_generator/timetable_outputs/DSAI_Sem3_SectionA_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/DSAI_Sem3_SectionA_Timetable.xlsx
@@ -468,28 +468,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DA261
-Statistical programing
-C101
-Dr.Ramesh Athe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>CS304
 Artificial intelligence
 C101
-Dr.Animesh chaturvedi</t>
-        </is>
-      </c>
+Dr.Animesh chaturvedi
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DA262
-Data Handaling and Visualization
-C101
-Dr. Siddharth</t>
+          <t>CS307
+Machine Learning
+C101
+Dr.Utkarsh Khaire
+[COMMON]</t>
         </is>
       </c>
     </row>
@@ -501,21 +496,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>CS307
+Machine Learning
+C101
+Dr.Utkarsh Khaire
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DA262
+Data Handaling and Visualization
+C101
+Dr. Siddharth
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>DA261
 Statistical programing
 C101
-Dr.Ramesh Athe</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CS307
-Machine Learning
-C101
-Dr.Utkarsh Khaire</t>
+Dr.Ramesh Athe
+[COMMON]</t>
         </is>
       </c>
     </row>
@@ -525,15 +530,32 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>HSS/IE
 Neuro-Linguistic Programming(NLP)
 C101
-Dr.Manjunath K V</t>
+Dr.Manjunath K V
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CS307
+Machine Learning
+C101
+Dr.Utkarsh Khaire
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DA261
+Statistical programing
+C101
+Dr.Ramesh Athe
+[COMMON]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -547,15 +569,17 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>CS304
 Artificial intelligence
 C101
-Dr.Animesh chaturvedi</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+Dr.Animesh chaturvedi
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -568,34 +592,22 @@
           <t>DA262
 Data Handaling and Visualization
 C101
-Dr. Siddharth</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CS307
-Machine Learning
-C101
-Dr.Utkarsh Khaire</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CS307
-Machine Learning
-C101
-Dr.Utkarsh Khaire</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+Dr. Siddharth
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>CS304
 Artificial intelligence
 C101
-Dr.Animesh chaturvedi</t>
-        </is>
-      </c>
+Dr.Animesh chaturvedi
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
